--- a/Dados/Hapvida-Estruturada(2).xlsx
+++ b/Dados/Hapvida-Estruturada(2).xlsx
@@ -227,8 +227,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="171" formatCode="[$R$ -416]#,##0.00"/>
-    <numFmt numFmtId="174" formatCode="&quot;R$&quot;#,##0.00"/>
+    <numFmt numFmtId="795" formatCode="[$R$ -416]#,##0.00"/>
+    <numFmt numFmtId="798" formatCode="&quot;R$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -344,7 +344,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="1" fillId="3" borderId="0" xfId="0">
+    <xf numFmtId="795" fontId="1" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0">
@@ -358,7 +358,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="3" borderId="0" xfId="0">
+    <xf numFmtId="795" fontId="1" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0">
@@ -370,7 +370,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="1" fillId="4" borderId="0" xfId="0">
+    <xf numFmtId="795" fontId="1" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0">
@@ -379,16 +379,16 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="2" fillId="3" borderId="0" xfId="0">
+    <xf numFmtId="798" fontId="2" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="174" fontId="2" fillId="4" borderId="0" xfId="0">
+    <xf numFmtId="798" fontId="2" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="174" fontId="2" fillId="3" borderId="0" xfId="0">
+    <xf numFmtId="798" fontId="2" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="174" fontId="2" fillId="4" borderId="0" xfId="0">
+    <xf numFmtId="798" fontId="2" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0">
@@ -399,7 +399,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0"/>
-    <xf numFmtId="171" fontId="3" fillId="3" borderId="0" xfId="0">
+    <xf numFmtId="795" fontId="3" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0">
@@ -739,7 +739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{26659903-A036-41F5-AC58-9A8FC335E114}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{8F027901-9686-4852-9267-30CD5FCC4353}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
